--- a/hisobotlar/rollar/2_Baza_Admin_Pasport_va_Shahodatnoma.xlsx
+++ b/hisobotlar/rollar/2_Baza_Admin_Pasport_va_Shahodatnoma.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>996810119</v>
+        <v>888480827</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>978550581</v>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
+        <v>902433774</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>885888187</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>902433774</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,9 @@
       <c r="F6" s="2" t="n">
         <v>953672602</v>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="n">
+        <v>906161560</v>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -734,8 +736,12 @@
           <t>AE1520971</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="F7" s="2" t="n">
+        <v>701202208</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>701252208</v>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -793,9 +799,11 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
+        <v>912177009</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>914606562</v>
       </c>
-      <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -853,9 +861,11 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
+        <v>874952608</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>973873803</v>
       </c>
-      <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
@@ -913,9 +923,11 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>943387727</v>
-      </c>
-      <c r="G10" s="2" t="n"/>
+        <v>918108191</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>900995763</v>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -972,8 +984,12 @@
           <t>AB9495274</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="2" t="n">
+        <v>883889326</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>996851321</v>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -1093,11 +1109,9 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>509071311</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>500331311</v>
-      </c>
+        <v>998191107</v>
+      </c>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -1215,10 +1229,10 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>936031585</v>
+        <v>976330414</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>882651585</v>
+        <v>914705957</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1276,12 +1290,8 @@
           <t>AE6171425</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>910707501</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>908698209</v>
-      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
@@ -1339,7 +1349,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>912240018</v>
+        <v>881236547</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="inlineStr">
@@ -1399,7 +1409,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>700343131</v>
+        <v>3431310</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
@@ -1459,9 +1469,11 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>770629890</v>
-      </c>
-      <c r="G19" s="2" t="n"/>
+        <v>706298900</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>973196260</v>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -1519,11 +1531,9 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>886177860</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>914577860</v>
-      </c>
+        <v>976190215</v>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
@@ -1645,7 +1655,9 @@
       <c r="F22" s="2" t="n">
         <v>870102621</v>
       </c>
-      <c r="G22" s="2" t="n"/>
+      <c r="G22" s="2" t="n">
+        <v>977011783</v>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -1705,7 +1717,9 @@
       <c r="F23" s="2" t="n">
         <v>875681508</v>
       </c>
-      <c r="G23" s="2" t="n"/>
+      <c r="G23" s="2" t="n">
+        <v>885857068</v>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -2009,9 +2023,11 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>880880124</v>
-      </c>
-      <c r="G28" s="2" t="n"/>
+        <v>808801240</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>156130020</v>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -2068,8 +2084,12 @@
           <t>AE5088010</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
+      <c r="F29" s="2" t="n">
+        <v>184403080</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>195942150</v>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
@@ -2126,8 +2146,12 @@
           <t>AB7137876</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="F30" s="2" t="n">
+        <v>721302400</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>861885800</v>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -2185,10 +2209,10 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>975855793</v>
+        <v>776070824</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>776070824</v>
+        <v>739901790</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2305,10 +2329,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
+        <v>701080829</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>992460829</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>701080829</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2427,10 +2451,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>908785105</v>
+        <v>87851050</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>916397685</v>
+        <v>163976850</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2488,7 +2512,9 @@
           <t>AE5324961</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n"/>
+      <c r="F36" s="2" t="n">
+        <v>906778076</v>
+      </c>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2547,7 +2573,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>976312909</v>
+        <v>163545560</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>953332960</v>
@@ -2669,11 +2695,9 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>770578758</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>704897375</v>
-      </c>
+        <v>915970964</v>
+      </c>
+      <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -2789,9 +2813,11 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>200132207</v>
-      </c>
-      <c r="G41" s="2" t="n"/>
+        <v>770850627</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>880850627</v>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -2909,10 +2935,10 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>885890027</v>
+        <v>885860697</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>957701169</v>
+        <v>885851406</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3031,10 +3057,10 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>916499228</v>
+        <v>914649228</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>976015200</v>
+        <v>886015200</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -3093,9 +3119,11 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>995658681</v>
-      </c>
-      <c r="G46" s="2" t="n"/>
+        <v>593907050</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>991437903</v>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -3152,12 +3180,8 @@
           <t>AE5293914</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>880669272</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>952556670</v>
-      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -3215,10 +3239,10 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>334948423</v>
+        <v>505010182</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>991840519</v>
+        <v>880780686</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -3280,7 +3304,7 @@
         <v>700720614</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>992558990</v>
+        <v>957741564</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -3339,9 +3363,11 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>880088028</v>
-      </c>
-      <c r="G50" s="2" t="n"/>
+        <v>700880280</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>880280880</v>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -3399,11 +3425,9 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>771219093</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>889770693</v>
-      </c>
+        <v>880790724</v>
+      </c>
+      <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -3639,9 +3663,11 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
+        <v>705180560</v>
+      </c>
+      <c r="G55" s="2" t="n">
         <v>997307709</v>
       </c>
-      <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
@@ -3823,10 +3849,10 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>999430596</v>
+        <v>593992050</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>959399205</v>
+        <v>523327660</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3885,9 +3911,11 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
+        <v>45042400</v>
+      </c>
+      <c r="G59" s="2" t="n">
         <v>939034744</v>
       </c>
-      <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -4123,10 +4151,10 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
+        <v>878006637</v>
+      </c>
+      <c r="G63" s="2" t="n">
         <v>970012780</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>973157721</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4247,11 +4275,9 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>876450108</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>990427984</v>
-      </c>
+        <v>904532125</v>
+      </c>
+      <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -4371,7 +4397,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>503019503</v>
+        <v>501582729</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>997304804</v>
@@ -4433,9 +4459,11 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>919595774</v>
-      </c>
-      <c r="G68" s="2" t="n"/>
+        <v>973872825</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>912184436</v>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -4737,11 +4765,9 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>885020703</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>880037679</v>
-      </c>
+        <v>940825116</v>
+      </c>
+      <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
@@ -4801,7 +4827,9 @@
       <c r="F74" s="2" t="n">
         <v>704785808</v>
       </c>
-      <c r="G74" s="2" t="n"/>
+      <c r="G74" s="2" t="n">
+        <v>887538486</v>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -4861,7 +4889,9 @@
       <c r="F75" s="2" t="n">
         <v>955838858</v>
       </c>
-      <c r="G75" s="2" t="n"/>
+      <c r="G75" s="2" t="n">
+        <v>916417532</v>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -4919,10 +4949,10 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
+        <v>874853608</v>
+      </c>
+      <c r="G76" s="2" t="n">
         <v>971880757</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>973810757</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4981,9 +5011,11 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>887611310</v>
-      </c>
-      <c r="G77" s="2" t="n"/>
+        <v>876113100</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>738982040</v>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -5165,10 +5197,10 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>888659008</v>
+        <v>898183800</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>881861712</v>
+        <v>883861712</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -5227,7 +5259,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>772254208</v>
+        <v>886199121</v>
       </c>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="inlineStr">
@@ -5287,10 +5319,10 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>908785105</v>
+        <v>862338080</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>916397685</v>
+        <v>770216705</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -5349,9 +5381,11 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
+        <v>951470825</v>
+      </c>
+      <c r="G83" s="2" t="n">
         <v>997422473</v>
       </c>
-      <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
@@ -5409,10 +5443,10 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
+        <v>880410227</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>881708081</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>880410227</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -5533,10 +5567,10 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>991312508</v>
+        <v>913125080</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>880068282</v>
+        <v>760782870</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -5595,9 +5629,11 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>930190686</v>
-      </c>
-      <c r="G87" s="2" t="n"/>
+        <v>33187080</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>11906860</v>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
@@ -5655,11 +5691,9 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>919483879</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>885967179</v>
-      </c>
+        <v>914636267</v>
+      </c>
+      <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -5717,7 +5751,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>875910918</v>
+        <v>759109180</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>885660802</v>
@@ -5779,9 +5813,11 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>906752661</v>
-      </c>
-      <c r="G90" s="2" t="n"/>
+        <v>763104770</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>732104770</v>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -5841,9 +5877,7 @@
       <c r="F91" s="2" t="n">
         <v>991863023</v>
       </c>
-      <c r="G91" s="2" t="n">
-        <v>952282462</v>
-      </c>
+      <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -5963,10 +5997,10 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>975890062</v>
+        <v>883889326</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>919561093</v>
+        <v>996851321</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -6087,9 +6121,11 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>995264709</v>
-      </c>
-      <c r="G95" s="2" t="n"/>
+        <v>834030080</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>952647090</v>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -6146,8 +6182,12 @@
           <t>AE4994200</t>
         </is>
       </c>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
+      <c r="F96" s="2" t="n">
+        <v>1114090</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>973891174</v>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -6205,10 +6245,10 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>904403666</v>
+        <v>44036660</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>912204218</v>
+        <v>122477210</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -6267,10 +6307,10 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>880306601</v>
+        <v>908152500</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>970874905</v>
+        <v>948170193</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -6329,9 +6369,11 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>505899948</v>
-      </c>
-      <c r="G99" s="2" t="n"/>
+        <v>914649228</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>886015200</v>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -6389,9 +6431,11 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>900709579</v>
-      </c>
-      <c r="G100" s="2" t="n"/>
+        <v>874637908</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>107095790</v>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -6449,11 +6493,9 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>991682082</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>770427406</v>
-      </c>
+        <v>976259907</v>
+      </c>
+      <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
@@ -6513,7 +6555,9 @@
       <c r="F102" s="2" t="n">
         <v>908841208</v>
       </c>
-      <c r="G102" s="2" t="n"/>
+      <c r="G102" s="2" t="n">
+        <v>919572717</v>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -6571,10 +6615,10 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>888270718</v>
+        <v>883879404</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>883860485</v>
+        <v>883813979</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -6693,7 +6737,9 @@
       <c r="F105" s="2" t="n">
         <v>908780280</v>
       </c>
-      <c r="G105" s="2" t="n"/>
+      <c r="G105" s="2" t="n">
+        <v>952694878</v>
+      </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -6873,9 +6919,11 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
+        <v>702902740</v>
+      </c>
+      <c r="G108" s="2" t="n">
         <v>882633833</v>
       </c>
-      <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -6933,10 +6981,10 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>885872701</v>
+        <v>858727010</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>910704107</v>
+        <v>68720885</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -6995,7 +7043,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>871160303</v>
+        <v>711603030</v>
       </c>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="inlineStr">
@@ -7119,7 +7167,9 @@
       <c r="F112" s="2" t="n">
         <v>879340301</v>
       </c>
-      <c r="G112" s="2" t="n"/>
+      <c r="G112" s="2" t="n">
+        <v>887228884</v>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -7177,10 +7227,10 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>976760905</v>
+        <v>888338593</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>876317371</v>
+        <v>888040691</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -7301,10 +7351,10 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>701202277</v>
+        <v>68161770</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>880096166</v>
+        <v>961660883</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -7425,10 +7475,10 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>908785105</v>
+        <v>331158083</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>916397685</v>
+        <v>976188380</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -7547,10 +7597,10 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>333890503</v>
+        <v>992216864</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>949791283</v>
+        <v>936660215</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -7609,10 +7659,10 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>876360708</v>
+        <v>912190617</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>976363774</v>
+        <v>912173481</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -7671,10 +7721,10 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>774231707</v>
+        <v>774321707</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>956162509</v>
+        <v>956163509</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -7736,7 +7786,7 @@
         <v>883090228</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>886177808</v>
+        <v>880057808</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -7795,7 +7845,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>914551195</v>
+        <v>887687008</v>
       </c>
       <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="inlineStr">
@@ -7855,11 +7905,9 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>881009504</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>976325574</v>
-      </c>
+        <v>880979477</v>
+      </c>
+      <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qamashi tumani</t>
@@ -7917,10 +7965,10 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>887381981</v>
+        <v>762945080</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>957401981</v>
+        <v>873819820</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -7979,10 +8027,10 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>886199703</v>
+        <v>818311670</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>876295108</v>
+        <v>183116787</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -8041,9 +8089,11 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>936367986</v>
-      </c>
-      <c r="G127" s="2" t="n"/>
+        <v>793476080</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>914564661</v>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -8161,7 +8211,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>978577404</v>
+        <v>978527404</v>
       </c>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="inlineStr">
@@ -8344,8 +8394,12 @@
           <t>AD7829399</t>
         </is>
       </c>
-      <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
+      <c r="F132" s="2" t="n">
+        <v>163545560</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>953332960</v>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -8403,9 +8457,11 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>886030021</v>
-      </c>
-      <c r="G133" s="2" t="n"/>
+        <v>912177009</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>914606562</v>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -8584,7 +8640,9 @@
           <t>AE7082532</t>
         </is>
       </c>
-      <c r="F136" s="2" t="n"/>
+      <c r="F136" s="2" t="n">
+        <v>910710283</v>
+      </c>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8825,10 +8883,10 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>995240810</v>
+        <v>991060810</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>955248180</v>
+        <v>955278180</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8887,10 +8945,10 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>773900314</v>
+        <v>796563080</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>779656308</v>
+        <v>713906770</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -8949,10 +9007,10 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
+        <v>918021670</v>
+      </c>
+      <c r="G142" s="2" t="n">
         <v>919614037</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>918021670</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -9011,10 +9069,10 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>908942471</v>
+        <v>943337608</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>919496471</v>
+        <v>943302274</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -9195,9 +9253,11 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
+        <v>778098230</v>
+      </c>
+      <c r="G146" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -9257,7 +9317,9 @@
       <c r="F147" s="2" t="n">
         <v>870004608</v>
       </c>
-      <c r="G147" s="2" t="n"/>
+      <c r="G147" s="2" t="n">
+        <v>771088048</v>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -9317,7 +9379,9 @@
       <c r="F148" s="2" t="n">
         <v>995590930</v>
       </c>
-      <c r="G148" s="2" t="n"/>
+      <c r="G148" s="2" t="n">
+        <v>951820195</v>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
@@ -9375,9 +9439,11 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>914551195</v>
-      </c>
-      <c r="G149" s="2" t="n"/>
+        <v>48913000</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>908708827</v>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
@@ -9435,10 +9501,10 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>903410676</v>
+        <v>189804950</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>918980495</v>
+        <v>88308650</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -9497,10 +9563,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>971100325</v>
+        <v>979054705</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>910710683</v>
+        <v>994192374</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9627,9 @@
       <c r="F152" s="2" t="n">
         <v>977997671</v>
       </c>
-      <c r="G152" s="2" t="n"/>
+      <c r="G152" s="2" t="n">
+        <v>884037671</v>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
@@ -9683,7 +9751,9 @@
       <c r="F154" s="2" t="n">
         <v>887886042</v>
       </c>
-      <c r="G154" s="2" t="n"/>
+      <c r="G154" s="2" t="n">
+        <v>883086042</v>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -9741,7 +9811,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>919490481</v>
+        <v>770428225</v>
       </c>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="inlineStr">
@@ -9921,10 +9991,10 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>950202813</v>
+        <v>502028130</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>950702813</v>
+        <v>727528130</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -10047,9 +10117,7 @@
       <c r="F160" s="2" t="n">
         <v>996739929</v>
       </c>
-      <c r="G160" s="2" t="n">
-        <v>973194003</v>
-      </c>
+      <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -10353,10 +10421,10 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
+        <v>877160130</v>
+      </c>
+      <c r="G165" s="2" t="n">
         <v>883887912</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>877160130</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -10475,9 +10543,11 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>876590027</v>
-      </c>
-      <c r="G167" s="2" t="n"/>
+        <v>765900270</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>707908680</v>
+      </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -10592,8 +10662,12 @@
           <t>AD9706738</t>
         </is>
       </c>
-      <c r="F169" s="2" t="n"/>
-      <c r="G169" s="2" t="n"/>
+      <c r="F169" s="2" t="n">
+        <v>738656120</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>738246060</v>
+      </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -10651,9 +10725,11 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>770683017</v>
-      </c>
-      <c r="G170" s="2" t="n"/>
+        <v>991284980</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>952310576</v>
+      </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -10835,9 +10911,11 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>976188504</v>
-      </c>
-      <c r="G173" s="2" t="n"/>
+        <v>886323773</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>914708493</v>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
@@ -10894,8 +10972,12 @@
           <t>AE4246251</t>
         </is>
       </c>
-      <c r="F174" s="2" t="n"/>
-      <c r="G174" s="2" t="n"/>
+      <c r="F174" s="2" t="n">
+        <v>50305390</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>919510536</v>
+      </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
@@ -11015,10 +11097,10 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>888191006</v>
+        <v>886061500</v>
       </c>
       <c r="G176" s="2" t="n">
-        <v>888606150</v>
+        <v>761500919</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -11076,8 +11158,12 @@
           <t>AB6304158</t>
         </is>
       </c>
-      <c r="F177" s="2" t="n"/>
-      <c r="G177" s="2" t="n"/>
+      <c r="F177" s="2" t="n">
+        <v>505895877</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>871947276</v>
+      </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
@@ -11135,7 +11221,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>931522577</v>
+        <v>315225770</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>770867725</v>
@@ -11318,8 +11404,12 @@
           <t>AE4385291</t>
         </is>
       </c>
-      <c r="F181" s="2" t="n"/>
-      <c r="G181" s="2" t="n"/>
+      <c r="F181" s="2" t="n">
+        <v>938918590</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>976350269</v>
+      </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qamashi tumani</t>
@@ -11377,10 +11467,10 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
+        <v>908810610</v>
+      </c>
+      <c r="G182" s="2" t="n">
         <v>908631674</v>
-      </c>
-      <c r="G182" s="2" t="n">
-        <v>908810610</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -11501,10 +11591,10 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>905181884</v>
+        <v>756130020</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>875613002</v>
+        <v>51818840</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>

--- a/hisobotlar/rollar/2_Baza_Admin_Pasport_va_Shahodatnoma.xlsx
+++ b/hisobotlar/rollar/2_Baza_Admin_Pasport_va_Shahodatnoma.xlsx
@@ -4330,14 +4330,22 @@
           <t>AB9205278</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
+      <c r="F62" s="2" t="n">
+        <v>992174752</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>955284081</v>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Alaqo'yliq MFY, Mevali ko'chasi, 109-uy</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
